--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486501_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486501_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2188</v>
+        <v>8.1494</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3964</v>
+        <v>7.1729</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8225</v>
+        <v>0.9766</v>
       </c>
       <c r="G2" t="n">
         <v>3.2259</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5498</v>
+        <v>-0.6192</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1286</v>
+        <v>-0.0949</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6784</v>
+        <v>-0.5242</v>
       </c>
       <c r="V2" t="n">
         <v>3.5851</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9261</v>
+        <v>4.1021</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4116</v>
+        <v>3.1925</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5145</v>
+        <v>0.9096</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5302</v>
+        <v>2.372</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0547</v>
+        <v>0.8484</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5849</v>
+        <v>1.5236</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6922</v>
+        <v>2.5977</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5575</v>
+        <v>1.3322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1347</v>
+        <v>1.2655</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.162</v>
+        <v>-0.2257</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6123</v>
+        <v>-0.4838</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4502</v>
+        <v>0.2582</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8276</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4606</v>
+        <v>0.4251</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6117</v>
+        <v>0.5948</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1511</v>
+        <v>-0.1698</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.713</v>
+        <v>3.5553</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0807</v>
+        <v>1.2566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6322</v>
+        <v>2.2987</v>
       </c>
       <c r="G4" t="n">
-        <v>2.372</v>
+        <v>1.5302</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8484</v>
+        <v>-0.0547</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5236</v>
+        <v>1.5849</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5977</v>
+        <v>1.6922</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3322</v>
+        <v>1.5575</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2655</v>
+        <v>0.1347</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2257</v>
+        <v>-0.162</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4838</v>
+        <v>-1.6123</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2582</v>
+        <v>1.4502</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0359</v>
+        <v>0.0898</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4831</v>
+        <v>0.4567</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4472</v>
+        <v>-0.3668</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5655</v>
+        <v>2.6368</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6759</v>
+        <v>1.1171</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8896</v>
+        <v>1.5197</v>
       </c>
       <c r="G5" t="n">
         <v>1.4377</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4334</v>
+        <v>0.5047</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2846</v>
+        <v>0.7258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1488</v>
+        <v>-0.2211</v>
       </c>
       <c r="V5" t="n">
         <v>2.4345</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1245</v>
+        <v>2.2266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1659</v>
+        <v>0.8365</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9586</v>
+        <v>1.3901</v>
       </c>
       <c r="G6" t="n">
         <v>3.7145</v>
@@ -922,13 +922,13 @@
         <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9799</v>
+        <v>-0.8778</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.0709</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2385</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9058</v>
+        <v>1.1077</v>
       </c>
       <c r="E7" t="n">
-        <v>1.647</v>
+        <v>0.722</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7411</v>
+        <v>0.3857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4944</v>
+        <v>0.6149</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6052</v>
+        <v>1.3958</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0996</v>
+        <v>-0.7809</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3352</v>
+        <v>0.9226</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2587</v>
+        <v>1.5147</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>-0.5921</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1592</v>
+        <v>-0.3077</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8639</v>
+        <v>-0.1188</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0231</v>
+        <v>-0.1889</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0411</v>
+        <v>-0.4218</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5516</v>
+        <v>-0.2007</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4896</v>
+        <v>-0.2211</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4997</v>
+        <v>-0.3904</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8272</v>
+        <v>0.5446</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3182</v>
+        <v>1.3457</v>
       </c>
       <c r="F8" t="n">
-        <v>0.509</v>
+        <v>-0.8011</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6149</v>
+        <v>-1.4266</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3958</v>
+        <v>-0.0974</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7809</v>
+        <v>-1.3291</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9226</v>
+        <v>-0.9747</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5147</v>
+        <v>0.0365</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5921</v>
+        <v>-1.0112</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3077</v>
+        <v>-0.4519</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1188</v>
+        <v>-0.1339</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1889</v>
+        <v>-0.318</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7023</v>
+        <v>-0.2235</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6044</v>
+        <v>0.018</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0978</v>
+        <v>-0.2415</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3904</v>
+        <v>2.6297</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3904</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4154</v>
+        <v>0.5079</v>
       </c>
       <c r="E9" t="n">
         <v>1.1857</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7703</v>
+        <v>-0.6778</v>
       </c>
       <c r="G9" t="n">
         <v>0.6518</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1293</v>
+        <v>0.4812</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0537</v>
+        <v>1.7154</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9244</v>
+        <v>-1.2343</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4266</v>
+        <v>0.4944</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0974</v>
+        <v>-0.6052</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3291</v>
+        <v>1.0996</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9747</v>
+        <v>0.3352</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0365</v>
+        <v>0.2587</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0112</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4519</v>
+        <v>0.1592</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1339</v>
+        <v>-0.8639</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.318</v>
+        <v>1.0231</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6388</v>
+        <v>0.6165</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>0.6201</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3648</v>
+        <v>-0.0036</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6297</v>
+        <v>-1.4997</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3899</v>
+        <v>0.7602</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7602</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>0.1724</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0987</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1787</v>
+        <v>0.2712</v>
       </c>
       <c r="G11" t="n">
         <v>0.0868</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2244</v>
+        <v>-0.1319</v>
       </c>
       <c r="T11" t="n">
         <v>-0.137</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.1091</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.7135</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9151</v>
+        <v>-0.8227</v>
       </c>
       <c r="G12" t="n">
         <v>0.1405</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7279</v>
+        <v>-0.9022</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0601</v>
+        <v>-0.2067</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.788</v>
+        <v>-0.6955</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9089</v>
+        <v>-0.9705</v>
       </c>
       <c r="E13" t="n">
         <v>-0.7831</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1258</v>
+        <v>-0.1874</v>
       </c>
       <c r="G13" t="n">
         <v>-0.989</v>
@@ -1468,13 +1468,13 @@
         <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0154</v>
+        <v>-0.0463</v>
       </c>
       <c r="T13" t="n">
         <v>-0.137</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1524</v>
+        <v>0.0907</v>
       </c>
       <c r="V13" t="n">
         <v>0.9347</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.0619</v>
+        <v>22.4044</v>
       </c>
       <c r="E14" t="n">
-        <v>18.0336</v>
+        <v>18.3761</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0284</v>
+        <v>4.028300000000001</v>
       </c>
       <c r="G14" t="n">
         <v>11.8531</v>
       </c>
       <c r="H14" t="n">
-        <v>2.067799999999999</v>
+        <v>2.0678</v>
       </c>
       <c r="I14" t="n">
         <v>9.785300000000001</v>
@@ -1522,22 +1522,22 @@
         <v>15.7551</v>
       </c>
       <c r="K14" t="n">
-        <v>8.2288</v>
+        <v>8.228799999999998</v>
       </c>
       <c r="L14" t="n">
         <v>7.5264</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.902</v>
+        <v>-3.901999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.161</v>
+        <v>-6.161000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>2.2586</v>
       </c>
       <c r="P14" t="n">
-        <v>3.262499999999999</v>
+        <v>3.2625</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.9627</v>
@@ -1546,16 +1546,16 @@
         <v>15.2254</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0731</v>
+        <v>-1.7305</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2259</v>
+        <v>1.5682</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.2988</v>
+        <v>-3.2987</v>
       </c>
       <c r="V14" t="n">
-        <v>9.0191</v>
+        <v>9.019099999999998</v>
       </c>
       <c r="W14" t="n">
         <v>13.0154</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1906</v>
+        <v>0.8521</v>
       </c>
       <c r="E15" t="n">
-        <v>1.49</v>
+        <v>0.3724</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7006</v>
+        <v>0.4797</v>
       </c>
       <c r="G15" t="n">
         <v>2.401</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4644</v>
+        <v>1.126</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8242</v>
+        <v>0.7066</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6402</v>
+        <v>0.4194</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9347</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3329</v>
+        <v>0.6861</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.117</v>
+        <v>-0.0052</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4499</v>
+        <v>0.6913</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9697</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1301</v>
+        <v>0.4834</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3115</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7486</v>
+        <v>-0.1194</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3886</v>
+        <v>-0.2283</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.1372</v>
+        <v>0.1088</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1274</v>
+        <v>2.1615</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2502</v>
+        <v>0.7239</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1227</v>
+        <v>1.4375</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6863</v>
+        <v>2.2532</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9596</v>
+        <v>0.6268</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7267</v>
+        <v>1.6264</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5589</v>
+        <v>-0.0917</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7094</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8495</v>
+        <v>-0.1889</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3338</v>
+        <v>0.1541</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0721</v>
+        <v>-0.3064</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4059</v>
+        <v>0.4605</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6297</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8079</v>
+        <v>-0.3516</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6753</v>
+        <v>3.7239</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1326</v>
+        <v>-4.0756</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1615</v>
+        <v>1.1274</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7239</v>
+        <v>1.2502</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4375</v>
+        <v>-0.1227</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2532</v>
+        <v>3.6863</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6268</v>
+        <v>2.9596</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6264</v>
+        <v>0.7267</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0917</v>
+        <v>-2.5589</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09710000000000001</v>
+        <v>-1.7094</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1889</v>
+        <v>-0.8495</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5344</v>
+        <v>0.0631</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.4074</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2191</v>
+        <v>-0.3443</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>-2.6297</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0394</v>
+        <v>-0.9405</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.0739</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.1334</v>
       </c>
       <c r="G19" t="n">
         <v>-3.284</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2021</v>
+        <v>0.301</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U19" t="n">
-        <v>0.005</v>
+        <v>0.2157</v>
       </c>
       <c r="V19" t="n">
         <v>2.2599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2742</v>
+        <v>-1.6413</v>
       </c>
       <c r="E20" t="n">
-        <v>0.102</v>
+        <v>-1.2767</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3762</v>
+        <v>-0.3646</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2544</v>
+        <v>-0.2706</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.539</v>
+        <v>0.3437</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2845</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0201</v>
+        <v>0.6865</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7086</v>
+        <v>0.6451</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6885</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2344</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8304</v>
+        <v>-0.3013</v>
       </c>
       <c r="O20" t="n">
-        <v>0.596</v>
+        <v>-0.6558</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5447</v>
+        <v>-0.2406</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0791</v>
+        <v>-0.2884</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5344</v>
+        <v>0.0478</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.9995</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7395</v>
+        <v>-0.3698</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2599</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3683</v>
+        <v>-2.5402</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9472</v>
+        <v>-0.3436</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4211</v>
+        <v>-2.1966</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2706</v>
+        <v>-2.1188</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3437</v>
+        <v>-1.0797</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.0391</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6865</v>
+        <v>0.3245</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6451</v>
+        <v>0.5141</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-2.4433</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3013</v>
+        <v>-1.5939</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-0.8495</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,28 +2092,28 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9677</v>
+        <v>0.1436</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9589</v>
+        <v>0.6369</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.4933</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4901</v>
+        <v>-2.7405</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2319</v>
+        <v>-0.4568</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2582</v>
+        <v>-2.2837</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1188</v>
+        <v>-0.2544</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0797</v>
+        <v>-1.539</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0391</v>
+        <v>1.2845</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3245</v>
+        <v>-0.0201</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5141</v>
+        <v>-0.7086</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1896</v>
+        <v>0.6885</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4433</v>
+        <v>-0.2344</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5939</v>
+        <v>-0.8304</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8495</v>
+        <v>0.596</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1937</v>
+        <v>0.0784</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7487</v>
+        <v>0.5203</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4419</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.9995</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9738</v>
+        <v>-4.0124</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0384</v>
+        <v>-2.2619</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9354</v>
+        <v>-1.7505</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2803</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2194</v>
+        <v>0.1809</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5432</v>
+        <v>0.3197</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3237</v>
+        <v>-0.1388</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3904</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.314</v>
+        <v>-4.7533</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6783</v>
+        <v>-0.9018</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6357</v>
+        <v>-3.8514</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6368</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0603</v>
+        <v>0.621</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8172</v>
+        <v>0.5936</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2431</v>
+        <v>0.0273</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.569</v>
+        <v>-5.7559</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3587</v>
+        <v>-1.5764</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2103</v>
+        <v>-4.1795</v>
       </c>
       <c r="G25" t="n">
         <v>-3.7283</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.906</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3305</v>
+        <v>0.4518</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5755</v>
+        <v>-0.5447</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4997</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.0618</v>
+        <v>-21.3169</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.0284</v>
+        <v>-4.0283</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.0335</v>
+        <v>-17.2887</v>
       </c>
       <c r="G26" t="n">
         <v>-11.853</v>
@@ -2482,13 +2482,13 @@
         <v>11.9626</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0728</v>
+        <v>2.8181</v>
       </c>
       <c r="T26" t="n">
-        <v>3.298800000000001</v>
+        <v>3.2987</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2258</v>
+        <v>-0.4807999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-9.0191</v>
